--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688769</v>
       </c>
       <c r="B2" t="n">
-        <v>58101</v>
+        <v>58105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129688768</v>
       </c>
       <c r="B3" t="n">
-        <v>57889</v>
+        <v>57893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129688765</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688769</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129688768</v>
       </c>
       <c r="B3" t="n">
-        <v>57893</v>
+        <v>57894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129688765</v>
       </c>
       <c r="B4" t="n">
-        <v>57865</v>
+        <v>57866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688768</v>
+        <v>129688765</v>
       </c>
       <c r="B3" t="n">
-        <v>57894</v>
+        <v>57866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>205976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,32 +905,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688765</v>
+        <v>129688768</v>
       </c>
       <c r="B4" t="n">
-        <v>57866</v>
+        <v>57894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205976</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688765</v>
+        <v>129688768</v>
       </c>
       <c r="B3" t="n">
-        <v>57866</v>
+        <v>57894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,32 +905,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688768</v>
+        <v>129688765</v>
       </c>
       <c r="B4" t="n">
-        <v>57894</v>
+        <v>57866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>205976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688769</v>
       </c>
       <c r="B2" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688765</v>
+        <v>129688768</v>
       </c>
       <c r="B3" t="n">
-        <v>57866</v>
+        <v>57893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,32 +905,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688768</v>
+        <v>129688765</v>
       </c>
       <c r="B4" t="n">
-        <v>57894</v>
+        <v>57866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>205976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688769</v>
       </c>
       <c r="B2" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129688768</v>
       </c>
       <c r="B3" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129688765</v>
       </c>
       <c r="B4" t="n">
-        <v>57866</v>
+        <v>57869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688769</v>
       </c>
       <c r="B2" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,32 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688768</v>
+        <v>129688765</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103020</v>
+        <v>205976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,32 +905,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688765</v>
+        <v>129688768</v>
       </c>
       <c r="B4" t="n">
-        <v>57869</v>
+        <v>57897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205976</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">

--- a/artfynd/A 52980-2025 artfynd.xlsx
+++ b/artfynd/A 52980-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688769</v>
       </c>
       <c r="B2" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129688768</v>
       </c>
       <c r="B3" t="n">
-        <v>57897</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,11 +908,11 @@
         <v>129688765</v>
       </c>
       <c r="B4" t="n">
-        <v>57870</v>
+        <v>58085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
